--- a/Employee_Reports_wi52/John Eric Bonganay Borcelis Q0474.xlsx
+++ b/Employee_Reports_wi52/John Eric Bonganay Borcelis Q0474.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -642,53 +642,53 @@
       <c r="K4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>CS-H9-TV (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-M-003</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>21-Aug-2024</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>21-Aug-2026</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1034,102 +1034,102 @@
       <c r="K12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Truck dock (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-M-006</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>21-Aug-2024</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>21-Aug-2026</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Cool Room (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-011</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>29-Sep-2024</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>29-Sep-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Cool Room (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-011</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>EQUIPMENT MANUAL</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>29-Sep-2024</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>29-Sep-2026</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-39</v>
+        <v>-47</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-39</v>
+        <v>-47</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-133</v>
+        <v>-141</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>-26</v>
+        <v>-34</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-33</v>
+        <v>-41</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>-26</v>
+        <v>-34</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1829,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-26</v>
+        <v>-34</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -1915,11 +1915,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
